--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -8,9 +8,21 @@
   </bookViews>
   <sheets>
     <sheet name="Proposals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workplan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Website Register" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Keywords" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Content Calendar" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Workflow Queue" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Workflows" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +30,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,9 +71,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,339 +440,1395 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Tracker ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Proposal name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Website link</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Matched keywords</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Why it matches</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Eligibility notes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recommended action</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Date found</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TENDERS – Public Procurement Regulatory Authority</t>
+          <t>4d6a73f007576d15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Request for Expression of Interest (EOI) for Pre-Verification and Certification at Source of Imported Categorised Equipment/Items; Collection of Advance Extended Producer Responsibility Fee (EPRF) and Designing of a Comprehensive In-Country Waste Collection and Management System</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://ppra.go.ke/category/tenders/</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Public Procurement Regulatory Authority</t>
-        </is>
+          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46010</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>training</t>
-        </is>
-      </c>
+          <t>National Environment Management Authority</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analytics, training</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The scope of work requires designing a digital waste management information/accounting system and delivering customizable training and knowledge transfer courses.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Requires at least 5 years of business experience, proof of registration, tax compliance, and reference to three similar assignments.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>25f534e2e5ff56b3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>National Environment Management Authority</t>
-        </is>
+          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46224</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>training</t>
-        </is>
-      </c>
+          <t>myGov Kenya</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analytics, training</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Explicitly requests the supply, implementation, training, and maintenance of a Virtual Assets Blockchain Analytics System.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Requires a tender security of KSHs. 900,000 and submissions must be made through the Electronic Government Procurement System (e-GPS).</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>3efd4b311816bf11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Kenya Reinsurance Corporation - Supply and Installation of Agentic AI Automation System</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-05-2025-2026-SUPPLY-DELIVERY-AND-INSTALLATION-OF-SMART-TV-SCREENS.pdf</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>National Environment Management Authority</t>
-        </is>
+          <t>https://gaa.go.ke/sites/default/files/2026-07/Kenya%20Reinsurance%20Corporation%20Limited%20Invitation%20to%20Tender.pdf</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46238</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>training</t>
-        </is>
-      </c>
+          <t>myGov Kenya</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>data science</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>The tender is for the supply and installation of an agentic AI automation system with Robotic Process Automation (RPA) integration, which is directly aligned with advanced data science and artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Requires tender security of Kshs. 500,000; opening date is August 4, 2026.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Tenders</t>
+          <t>805b441e54acb380</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Open University of Kenya Supplier Prequalification 2026–2028</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/all-tenders#main-content</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
+          <t>https://gaa.go.ke/sites/default/files/2026-08/%20Open%20University%20of%20Kenya%20Tender%20Notice.pdf</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>myGov Kenya</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Category OUK/026/OP/2026-2028 explicitly seeks providers for ICT Management Consulting, ICT Systems Audit, and 'Training on ICT Security Solutions'.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>The specified training category (OUK/026/OP/2026-2028) is under the 'Open Category', meaning it is open to all interested and eligible firms.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Due date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Provide and prioritise source website links</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Add approved ministry and donor portals to the source intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Confirm keywords and exclusion terms</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Source list</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Confirm analytics, data science, training, and exclusion terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Add approved sources and complete a test scrape</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Technical owner</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Olivia source links</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Activate and validate each source before recurring monitoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Configure Tuesday/Thursday myGov alert recipient</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Olivia / Technical owner</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46251</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>myGov Kenya</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>analytics, training</t>
+          <t>SMTP access</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Set alert recipient and SMTP details in .env.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>All Tenders</t>
+          <t>Review new opportunities and assign a proposal owner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://gaa.go.ke/all-tenders</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>46256</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>myGov Kenya</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>analytics, training</t>
+          <t>Proposal tracker</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Update proposal status, owner, and notes after each scan.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System.pdf</t>
+          <t>Define content-folder approval and posting workflow</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
+          <t>Olivia / Content owner</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>46258</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>myGov Kenya</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>analytics, training</t>
+          <t>Content folder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Confirm approval steps before connecting posting automation.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Review performance and refine keywords</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Two weeks of results</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Remove irrelevant results and add useful new terms.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Website URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Check frequency</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>myGov Kenya</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://gaa.go.ke/all-tenders</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mygov</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tuesday and Thursday</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Public Procurement Information Portal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://tenders.go.ke/tenders</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>national_procurement_portal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Weekdays</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Verified reachable, but tender entries are JavaScript-rendered and require a browser-based source adapter before activation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kenya Revenue Authority</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.kra.go.ke/tenders</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>government_agency</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Weekdays</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>National Environment Management Authority</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/tenders/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>government_agency</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Weekdays</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Public Procurement Regulatory Authority</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://ppra.go.ke/category/tenders/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>government_agency</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Weekdays</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Include / Exclude</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>data science</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>National Environment Management Authority</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>training</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>loading...</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://ppra.go.ke/standard-tender-documents/</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Public Procurement Regulatory Authority</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>training</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Open University of Kenya Tender Notice.pdf</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Content item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Approval status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Posting date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tracker ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Next action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Review due date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>805b441e54acb380</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Open University of Kenya Supplier Prequalification 2026–2028</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://gaa.go.ke/sites/default/files/2026-08/%20Open%20University%20of%20Kenya%20Tender%20Notice.pdf</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>myGov Kenya</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>training</t>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3efd4b311816bf11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kenya Reinsurance Corporation - Supply and Installation of Agentic AI Automation System</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://gaa.go.ke/sites/default/files/2026-07/Kenya%20Reinsurance%20Corporation%20Limited%20Invitation%20to%20Tender.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4d6a73f007576d15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Request for Expression of Interest (EOI) for Pre-Verification and Certification at Source of Imported Categorised Equipment/Items; Collection of Advance Extended Producer Responsibility Fee (EPRF) and Designing of a Comprehensive In-Country Waste Collection and Management System</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>25f534e2e5ff56b3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Automated action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Output / escalation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Proposal discovery</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Scheduled monitoring finds a keyword match</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Create or update a persistent review task</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Workflow Queue; review due date is three days before tender close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>myGov alert</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tuesday/Thursday scheduler finds new matches</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Send one email per new opportunity</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Scheduler waits for SMTP configuration and prevents repeat alerts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Proposal review</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Workflow Queue contains Review required</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Assess relevance and set bid decision</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Proposal owner</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Update the workflow state using the command below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Content publishing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Content receives approval</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Queue item for posting automation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Content owner</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>To be connected when the content folder/platform is provided.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Workflows" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -451,8 +451,8 @@
     <col width="43" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4d6a73f007576d15</t>
+          <t>b9d78cdc0f20072d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Request for Expression of Interest (EOI) for Pre-Verification and Certification at Source of Imported Categorised Equipment/Items; Collection of Advance Extended Producer Responsibility Fee (EPRF) and Designing of a Comprehensive In-Country Waste Collection and Management System</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>analytics, training</t>
+          <t>training</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The scope of work requires designing a digital waste management information/accounting system and delivering customizable training and knowledge transfer courses.</t>
+          <t>Matched configured keyword(s): training.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Requires at least 5 years of business experience, proof of registration, tax compliance, and reference to three similar assignments.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -609,55 +609,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25f534e2e5ff56b3</t>
+          <t>05ecf7d703f4ee05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-05-2025-2026-SUPPLY-DELIVERY-AND-INSTALLATION-OF-SMART-TV-SCREENS.pdf</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46224</v>
+        <v>46104</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>myGov Kenya</t>
+          <t>National Environment Management Authority</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>analytics, training</t>
+          <t>training</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Explicitly requests the supply, implementation, training, and maintenance of a Virtual Assets Blockchain Analytics System.</t>
+          <t>Matched configured keyword(s): training.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Requires a tender security of KSHs. 900,000 and submissions must be made through the Electronic Government Procurement System (e-GPS).</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pursue</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -678,26 +678,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3efd4b311816bf11</t>
+          <t>91b402a21c251619</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kenya Reinsurance Corporation - Supply and Installation of Agentic AI Automation System</t>
+          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Kenya%20Reinsurance%20Corporation%20Limited%20Invitation%20to%20Tender.pdf</t>
+          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46238</v>
+        <v>46224</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -706,22 +706,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>analytics, training</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The tender is for the supply and installation of an agentic AI automation system with Robotic Process Automation (RPA) integration, which is directly aligned with advanced data science and artificial intelligence.</t>
+          <t>Matched configured keyword(s): analytics, training.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Requires tender security of Kshs. 500,000; opening date is August 4, 2026.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>805b441e54acb380</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Open University of Kenya Supplier Prequalification 2026–2028</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -780,22 +780,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Category OUK/026/OP/2026-2028 explicitly seeks providers for ICT Management Consulting, ICT Systems Audit, and 'Training on ICT Security Solutions'.</t>
+          <t>Matched configured keyword(s): training.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The specified training category (OUK/026/OP/2026-2028) is under the 'Open Category', meaning it is open to all interested and eligible firms.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Pursue</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -813,8 +813,150 @@
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6b3a427e52bb058c</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>National Environment Management Authority</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Matched configured keyword(s): training.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fd4720ea6610ff8d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>loading...</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://ppra.go.ke/standard-tender-documents</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Public Procurement Regulatory Authority</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Matched configured keyword(s): training.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O5"/>
+  <autoFilter ref="A1:O7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1113,11 +1255,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -1311,8 +1453,124 @@
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://example.gov/tenders</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-10T09:15:56.399Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://example.org/funding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-10T09:15:56.399Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-10T10:04:59.643Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-10T10:11:01.745Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1481,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1533,12 +1791,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>805b441e54acb380</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Supplier Prequalification 2026–2028</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1568,12 +1826,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3efd4b311816bf11</t>
+          <t>91b402a21c251619</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kenya Reinsurance Corporation - Supply and Installation of Agentic AI Automation System</t>
+          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1587,7 +1845,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1596,19 +1854,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Kenya%20Reinsurance%20Corporation%20Limited%20Invitation%20to%20Tender.pdf</t>
+          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4d6a73f007576d15</t>
+          <t>6b3a427e52bb058c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Request for Expression of Interest (EOI) for Pre-Verification and Certification at Source of Imported Categorised Equipment/Items; Collection of Advance Extended Producer Responsibility Fee (EPRF) and Designing of a Comprehensive In-Country Waste Collection and Management System</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1631,19 +1889,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25f534e2e5ff56b3</t>
+          <t>05ecf7d703f4ee05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1657,21 +1915,91 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-05-2025-2026-SUPPLY-DELIVERY-AND-INSTALLATION-OF-SMART-TV-SCREENS.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b9d78cdc0f20072d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fd4720ea6610ff8d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>loading...</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>46244</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Review required</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://ppra.go.ke/standard-tender-documents</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -18,8 +18,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
@@ -449,9 +449,9 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
     <col width="54" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>b9d78cdc0f20072d</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -555,15 +555,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+          <t>https://gaa.go.ke/sites/default/files/2026-08/%20Open%20University%20of%20Kenya%20Tender%20Notice.pdf</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46010</v>
+        <v>46254</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>National Environment Management Authority</t>
+          <t>myGov Kenya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Matched configured keyword(s): training.</t>
+          <t>Matched configured ICT keyword(s): training.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -609,45 +609,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05ecf7d703f4ee05</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-05-2025-2026-SUPPLY-DELIVERY-AND-INSTALLATION-OF-SMART-TV-SCREENS.pdf</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>46104</v>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>National Environment Management Authority</t>
+          <t>climatechange.ai</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>analysis, machine learning, training</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Matched configured keyword(s): training.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, training.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,45 +680,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>91b402a21c251619</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System.pdf</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>46224</v>
+          <t>https://www.climatechange.ai/calls</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>myGov Kenya</t>
+          <t>climatechange.ai</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>analytics, training</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Matched configured keyword(s): analytics, training.</t>
+          <t>Matched configured ICT keyword(s): machine learning.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -747,45 +751,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bc97777e6c0833cb</t>
+          <t>17124d19bfc6b3cd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice.pdf</t>
+          <t>Climate Change AI Innovation Grants</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-08/%20Open%20University%20of%20Kenya%20Tender%20Notice.pdf</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>46254</v>
+          <t>https://www.climatechange.ai/innovation_grants</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>myGov Kenya</t>
+          <t>climatechange.ai</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>analysis, machine learning, artificial intelligence, training</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Matched configured keyword(s): training.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -816,17 +822,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6b3a427e52bb058c</t>
+          <t>55b4d62ba31143e7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>NATIONAL ENVIRONMENT MANAGEMENT AUTHORITY (NEMA) OPEN NATIONAL TENDER SUPPLY, DELIVERY, INSTALLATION AND COMMISSIONING OF LABORATORY EQUIPMENT TENDER REF. NO. N</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -846,17 +852,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>analysis, analytical, training</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Matched configured keyword(s): training.</t>
+          <t>Matched configured ICT keyword(s): analysis, analytical, training.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -887,12 +893,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fd4720ea6610ff8d</t>
+          <t>9b0fded721a6ff45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>loading...</t>
+          <t>Standard Tender Documents – Public Procurement Regulatory Authority × Close Close × Close Close × Close loading... File Properties Name File Uploader Folder PPA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +933,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Matched configured keyword(s): training.</t>
+          <t>Matched configured ICT keyword(s): training.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1255,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1456,60 +1462,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>User submitted</t>
+          <t>bluedot-network.org</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://example.gov/tenders</t>
+          <t>https://www.bluedot-network.org/certification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pending review</t>
+          <t>approved_submission</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Every monitor run</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>User submitted</t>
+          <t>climatechange.ai</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://example.org/funding</t>
+          <t>https://www.climatechange.ai/</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pending review</t>
+          <t>approved_submission</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Every monitor run</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1519,7 +1525,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
+          <t>https://example.gov/tenders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1536,7 +1542,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-10T10:04:59.643Z</t>
+          <t>Submitted 2026-08-10T09:15:56.399Z</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
+          <t>https://example.org/funding</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1565,12 +1571,128 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Submitted 2026-08-10T09:15:56.399Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-10T10:04:59.643Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Submitted 2026-08-10T10:11:01.745Z</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.bluedot-network.org/certification</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-11T16:20:04.680Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-11T18:24:37.612Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1581,11 +1703,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1615,7 +1737,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1633,12 +1755,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1651,23 +1773,311 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>analytical</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>data analysis</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>data analytics</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>data science</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>data scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data-scientist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>machine learning</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>artificial intelligence</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data science</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>training</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ICT training</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>grant application</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>funding opportunity</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>certification offer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>certification application</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>apply for certification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>paper proposal</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Paper proposal</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>call for papers</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Paper proposal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:D20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1826,12 +2236,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>91b402a21c251619</t>
+          <t>55b4d62ba31143e7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital Markets Authority Tender Notice for Supply, Implementation, Training and Maintenance of a Virtual Assets Blockchain Analytics System.pdf</t>
+          <t>NATIONAL ENVIRONMENT MANAGEMENT AUTHORITY (NEMA) OPEN NATIONAL TENDER SUPPLY, DELIVERY, INSTALLATION AND COMMISSIONING OF LABORATORY EQUIPMENT TENDER REF. NO. N</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1845,7 +2255,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1854,19 +2264,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://gaa.go.ke/sites/default/files/2026-07/Capital%20Markets%20Authority%20Tender%20Notice%20for%20Supply%2C%20Implementation%2C%20Training%20and%20Maintenance%20of%20a%20Virtual%20Assets%20Blockchain%20Analytics%20System.pdf</t>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6b3a427e52bb058c</t>
+          <t>9b0fded721a6ff45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Standard Tender Documents – Public Procurement Regulatory Authority × Close Close × Close Close × Close loading... File Properties Name File Uploader Folder PPA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1880,7 +2290,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1889,19 +2299,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
+          <t>https://ppra.go.ke/standard-tender-documents</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05ecf7d703f4ee05</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1915,7 +2325,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1924,19 +2334,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-05-2025-2026-SUPPLY-DELIVERY-AND-INSTALLATION-OF-SMART-TV-SCREENS.pdf</t>
+          <t>https://www.climatechange.ai/calls</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b9d78cdc0f20072d</t>
+          <t>17124d19bfc6b3cd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Climate Change AI Innovation Grants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1950,7 +2360,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1959,19 +2369,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2025/12/Tender-no.-NEMAEOI012025-2026_EOI_International-Tender.pdf</t>
+          <t>https://www.climatechange.ai/innovation_grants</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fd4720ea6610ff8d</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>loading...</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1985,7 +2395,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1994,7 +2404,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://ppra.go.ke/standard-tender-documents</t>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
         </is>
       </c>
     </row>

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Workflows" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,12 +440,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -602,29 +602,29 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aa16da3072f3ff5b</t>
+          <t>166f9b27c5e956f4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
+          <t>https://www.bluedot-network.org/certification</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -634,22 +634,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>climatechange.ai</t>
+          <t>bluedot-network.org</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>analysis, machine learning, training</t>
+          <t>apply for certification</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): analysis, machine learning, training.</t>
+          <t>Matched configured ICT keyword(s): apply for certification.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f7683a8e4ad35977</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climate Change AI Grant Calls</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/calls</t>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -710,17 +710,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>analysis, machine learning, training</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): machine learning.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, training.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -744,19 +744,19 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17124d19bfc6b3cd</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/innovation_grants</t>
+          <t>https://www.climatechange.ai/calls</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>analysis, machine learning, artificial intelligence, training</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
+          <t>Matched configured ICT keyword(s): machine learning.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -815,29 +815,29 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>55b4d62ba31143e7</t>
+          <t>17124d19bfc6b3cd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NATIONAL ENVIRONMENT MANAGEMENT AUTHORITY (NEMA) OPEN NATIONAL TENDER SUPPLY, DELIVERY, INSTALLATION AND COMMISSIONING OF LABORATORY EQUIPMENT TENDER REF. NO. N</t>
+          <t>Climate Change AI Innovation Grants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
+          <t>https://www.climatechange.ai/innovation_grants</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>National Environment Management Authority</t>
+          <t>climatechange.ai</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>analysis, analytical, training</t>
+          <t>analysis, machine learning, artificial intelligence, training</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): analysis, analytical, training.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -886,83 +886,225 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>55b4d62ba31143e7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NATIONAL ENVIRONMENT MANAGEMENT AUTHORITY (NEMA) OPEN NATIONAL TENDER SUPPLY, DELIVERY, INSTALLATION AND COMMISSIONING OF LABORATORY EQUIPMENT TENDER REF. NO. N</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nema.go.ke/wp-content/uploads/2026/03/TENDER-NO-NEMA-T-04-2025-2026-Tender-Supply-DeliveryInstallation-and-Commissioning-of-Laboratory-Equipment.pdf</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>National Environment Management Authority</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analysis, analytical, training</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Matched configured ICT keyword(s): analysis, analytical, training.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3c2462dbed3db6a6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OECD InfraDays 2026 Highlights the Growing Global Momentum Behind Blue Dot Network Certification</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.bluedot-network.org/news/bdn-certificationceremony</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>bluedot-network.org</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply for certification</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Matched configured ICT keyword(s): apply for certification.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Review source document for eligibility requirements.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>9b0fded721a6ff45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Standard Tender Documents – Public Procurement Regulatory Authority × Close Close × Close Close × Close loading... File Properties Name File Uploader Folder PPA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://ppra.go.ke/standard-tender-documents</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Public Procurement Regulatory Authority</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>training</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Matched configured ICT keyword(s): training.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Review required</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Project team</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="N9" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O7"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1034,10 +1176,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1063,10 +1205,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1096,10 +1238,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1129,10 +1271,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1304,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1195,10 +1337,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1228,10 +1370,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1261,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1520,31 +1662,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>User submitted</t>
+          <t>bluedot-network.org</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://example.gov/tenders</t>
+          <t>https://www.bluedot-network.org/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pending review</t>
+          <t>managed_source</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Every monitor run</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1554,7 +1696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://example.org/funding</t>
+          <t>https://example.gov/tenders</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1583,7 +1725,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
+          <t>https://example.org/funding</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1600,7 +1742,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-10T10:04:59.643Z</t>
+          <t>Submitted 2026-08-10T09:15:56.399Z</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1754,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
+          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1629,7 +1771,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-10T10:11:01.745Z</t>
+          <t>Submitted 2026-08-10T10:04:59.643Z</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1783,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.bluedot-network.org/certification</t>
+          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1658,7 +1800,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-11T16:20:04.680Z</t>
+          <t>Submitted 2026-08-10T10:11:01.745Z</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1812,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/</t>
+          <t>https://www.bluedot-network.org/certification</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1687,12 +1829,70 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Submitted 2026-08-11T16:20:04.680Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.climatechange.ai/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Submitted 2026-08-11T18:24:37.612Z</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>User submitted</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/study/international-students/countries/africa/kenya?utm_source=google-search&amp;utm_medium=paid&amp;utm_campaign=international-recruitment-2026&amp;utm_content=brand_ug-pg-ke&amp;gad_source=1&amp;gad_campaignid=22138204529&amp;gbraid=0AAAAA-Jv9mK-HMbYwd0xUiIwJsYXujvIu&amp;gclid=CjwKCAjw4dDTBhAqEiwAkHYmSix5GlL4etFz30Inndq4q0FUkb21c040s1XsfJ6nm0XAcefOUWDscRoCxsgQAvD_BwE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pending review</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-11T19:52:46.857Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2149,7 +2349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2408,8 +2608,78 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>166f9b27c5e956f4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.bluedot-network.org/certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3c2462dbed3db6a6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OECD InfraDays 2026 Highlights the Growing Global Momentum Behind Blue Dot Network Certification</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Review proposal and assign a bid decision</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Project team</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.bluedot-network.org/news/bdn-certificationceremony</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
@@ -445,14 +445,14 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="54" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bc97777e6c0833cb</t>
+          <t>17b2c29e5c65d88f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice.pdf</t>
+          <t>Open University of Kenya Prequalification of Suppliers (2026-2028)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>training, ICT training</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): training.</t>
+          <t>The tender prequalification includes dedicated categories for 'Provision of ICT Management Consulting, ICT Systems Audit and Training on ICT Security Solutions' and 'Consultancy on E-Learning and Online Systems'.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Open to all interested and eligible firms. Certain reserved categories are restricted to AGPO groups (Youth, Women, and PWDs) with a valid AGPO certificate.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -609,19 +609,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>166f9b27c5e956f4</t>
+          <t>28f70fbc788b8104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Blue Dot Network (BDN) Certification</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bluedot-network.org/certification</t>
@@ -639,7 +639,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>apply for certification</t>
+          <t>certification offer, certification application, apply for certification</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): apply for certification.</t>
+          <t>Offers an official certification process for global infrastructure projects, which explicitly includes the ICT sector.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Applies to infrastructure projects across energy, water, transport, and ICT, under various delivery and ownership models.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Digital Health &amp; Climate Tech</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning, artificial intelligence, grant application, funding opportunity</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): machine learning.</t>
+          <t>The platform outlines grant funding programs designed to catalyze research and dataset creation at the intersection of climate change and machine learning.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Collaborations between academic researchers, non-profits, startups, and governmental organizations globally.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -822,17 +822,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17124d19bfc6b3cd</t>
+          <t>9686535c456d1a83</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants</t>
+          <t>Climate Change AI Innovation Grants Program</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Digital Health &amp; Climate Tech</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>analysis, machine learning, artificial intelligence, training</t>
+          <t>machine learning, artificial intelligence, data analysis, data science, grant application, funding opportunity</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
+          <t>The program awards seed grants of up to $150K for projects deploying machine learning, data science, and AI tools to address climate change challenges.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Academic researchers, non-profits, startups, and governmental organizations seeking to build partnerships and public datasets. No active call is currently open, but proposals are kept on file.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1903,11 +1903,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2276,8 +2276,188 @@
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>digital health Africa grant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Digital Health &amp; Climate Tech</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI healthcare Africa funding</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Digital Health &amp; Climate Tech</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>telemedicine Africa grant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Digital Health &amp; Climate Tech</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate technology Africa funding</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Digital Health &amp; Climate Tech</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>smart cities Africa grant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Digital Health &amp; Climate Tech</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>youth employment Africa grant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Youth, Women &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>youth digital skills Africa funding</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Youth, Women &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>women in technology Africa funding</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Youth, Women &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>women in STEM Africa grant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Youth, Women &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>gender inclusion digital Africa grant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Youth, Women &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D20"/>
+  <autoFilter ref="A1:D30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2401,12 +2581,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bc97777e6c0833cb</t>
+          <t>17b2c29e5c65d88f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice.pdf</t>
+          <t>Open University of Kenya Prequalification of Suppliers (2026-2028)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2541,12 +2721,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17124d19bfc6b3cd</t>
+          <t>9686535c456d1a83</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants</t>
+          <t>Climate Change AI Innovation Grants Program</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2560,7 +2740,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2611,12 +2791,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>166f9b27c5e956f4</t>
+          <t>28f70fbc788b8104</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Blue Dot Network (BDN) Certification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17b2c29e5c65d88f</t>
+          <t>7b06c862b59f701e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Prequalification of Suppliers (2026-2028)</t>
+          <t>Open University of Kenya Tender Notice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The tender prequalification includes dedicated categories for 'Provision of ICT Management Consulting, ICT Systems Audit and Training on ICT Security Solutions' and 'Consultancy on E-Learning and Online Systems'.</t>
+          <t>Invites registration and prequalification for several ICT-related categories including e-learning systems consultancy, ICT management consulting, and training on ICT security solutions.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open to all interested and eligible firms. Certain reserved categories are restricted to AGPO groups (Youth, Women, and PWDs) with a valid AGPO certificate.</t>
+          <t>Open to all interested and eligible firms; must submit completed physical prequalification documents to Konza Technopolis.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Pursue</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28f70fbc788b8104</t>
+          <t>9cca09bd6a8caab0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blue Dot Network (BDN) Certification</t>
+          <t>Blue Dot Network Certification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>certification offer, certification application, apply for certification</t>
+          <t>certification application, apply for certification, certification offer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Offers an official certification process for global infrastructure projects, which explicitly includes the ICT sector.</t>
+          <t>Provides a certification pathway for major infrastructure projects, explicitly including those in the ICT sector.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Applies to infrastructure projects across energy, water, transport, and ICT, under various delivery and ownership models.</t>
+          <t>Open to projects across different life cycle stages (planning to operations) and various delivery models. Must meet robust international standards across 10 elements.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9686535c456d1a83</t>
+          <t>17124d19bfc6b3cd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants Program</t>
+          <t>Climate Change AI Innovation Grants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, data analysis, data science, grant application, funding opportunity</t>
+          <t>grant application, funding opportunity, artificial intelligence, machine learning</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The program awards seed grants of up to $150K for projects deploying machine learning, data science, and AI tools to address climate change challenges.</t>
+          <t>A seed grant program focusing on the development of AI/ML tools, datasets, and systems to address climate change mitigation and adaptation.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Academic researchers, non-profits, startups, and governmental organizations seeking to build partnerships and public datasets. No active call is currently open, but proposals are kept on file.</t>
+          <t>Allocates seed grants typically up to $150K for projects of one year in duration. No current active calls, but accepts partnership inquiries.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2581,12 +2581,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17b2c29e5c65d88f</t>
+          <t>7b06c862b59f701e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Prequalification of Suppliers (2026-2028)</t>
+          <t>Open University of Kenya Tender Notice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9686535c456d1a83</t>
+          <t>17124d19bfc6b3cd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants Program</t>
+          <t>Climate Change AI Innovation Grants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28f70fbc788b8104</t>
+          <t>9cca09bd6a8caab0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Dot Network (BDN) Certification</t>
+          <t>Blue Dot Network Certification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7b06c862b59f701e</t>
+          <t>8d40238686713191</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice</t>
+          <t>Open University of Kenya Supplier Prequalification (2026-2028)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Invites registration and prequalification for several ICT-related categories including e-learning systems consultancy, ICT management consulting, and training on ICT security solutions.</t>
+          <t>Tender notice includes a specific open category (OUK/026/OP/2026-2028) for the provision of ICT Management Consulting, ICT Systems Audit, and Training on ICT Security Solutions.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open to all interested and eligible firms; must submit completed physical prequalification documents to Konza Technopolis.</t>
+          <t>Open to all eligible firms. Prequalification documents must be downloaded from the website and physically deposited by Thursday, 20th August 2026, 11:30 AM East African Time.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9cca09bd6a8caab0</t>
+          <t>166f9b27c5e956f4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blue Dot Network Certification</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>certification application, apply for certification, certification offer</t>
+          <t>apply for certification</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Provides a certification pathway for major infrastructure projects, explicitly including those in the ICT sector.</t>
+          <t>Matched configured ICT keyword(s): apply for certification.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Open to projects across different life cycle stages (planning to operations) and various delivery models. Must meet robust international standards across 10 elements.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O3" t="inlineStr"/>
     </row>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O4" t="inlineStr"/>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, grant application, funding opportunity</t>
+          <t>machine learning, artificial intelligence, grant application, funding opportunity, climate technology Africa funding</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The platform outlines grant funding programs designed to catalyze research and dataset creation at the intersection of climate change and machine learning.</t>
+          <t>Provides grant opportunities at the intersection of climate change and machine learning/AI, which aligns with climate technology funding keywords.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Collaborations between academic researchers, non-profits, startups, and governmental organizations globally.</t>
+          <t>Supports research, deployment, and dataset creation. Eligibility varies per specific call (some past calls were Africa-focused).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
@@ -852,22 +852,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>grant application, funding opportunity, artificial intelligence, machine learning</t>
+          <t>artificial intelligence, machine learning, grant application, funding opportunity</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A seed grant program focusing on the development of AI/ML tools, datasets, and systems to address climate change mitigation and adaptation.</t>
+          <t>Provides seed funding of up to $150K for projects leveraging artificial intelligence and machine learning to tackle climate change mitigation and adaptation.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Allocates seed grants typically up to $150K for projects of one year in duration. No current active calls, but accepts partnership inquiries.</t>
+          <t>Aims to build partnerships between academic researchers, non-profits, startups, and other companies. Currently has no active/future calls planned.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2581,12 +2581,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7b06c862b59f701e</t>
+          <t>8d40238686713191</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice</t>
+          <t>Open University of Kenya Supplier Prequalification (2026-2028)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2791,12 +2791,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9cca09bd6a8caab0</t>
+          <t>166f9b27c5e956f4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Dot Network Certification</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -578,12 +578,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tender notice includes a specific open category (OUK/026/OP/2026-2028) for the provision of ICT Management Consulting, ICT Systems Audit, and Training on ICT Security Solutions.</t>
+          <t>Tender includes specific open categories for ICT system procurement, software, LAN/WAN services, and training on ICT security solutions.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open to all eligible firms. Prequalification documents must be downloaded from the website and physically deposited by Thursday, 20th August 2026, 11:30 AM East African Time.</t>
+          <t>Open to eligible firms; includes reserved categories for AGPO groups (Youth, Women, and PWDs) with a valid AGPO certificate.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -609,19 +609,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>166f9b27c5e956f4</t>
+          <t>9cca09bd6a8caab0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Blue Dot Network Certification</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bluedot-network.org/certification</t>
@@ -639,7 +639,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>apply for certification</t>
+          <t>apply for certification, certification application, certification offer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): apply for certification.</t>
+          <t>Offers a certification framework and application process for infrastructure projects, which explicitly includes the ICT sector.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Open to infrastructure projects across major sectors, including ICT, at various lifecycle stages and ownership models.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, grant application, funding opportunity, climate technology Africa funding</t>
+          <t>machine learning, artificial intelligence, climate technology Africa funding, grant application</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Provides grant opportunities at the intersection of climate change and machine learning/AI, which aligns with climate technology funding keywords.</t>
+          <t>Active grant program supporting research and deployment at the intersection of climate change and machine learning.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Supports research, deployment, and dataset creation. Eligibility varies per specific call (some past calls were Africa-focused).</t>
+          <t>Supports impactful projects involving dataset creation, deployment, and research utilizing ML to tackle climate change.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Digital Health &amp; Climate Tech</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>artificial intelligence, machine learning, grant application, funding opportunity</t>
+          <t>grant application, funding opportunity, machine learning, artificial intelligence</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Provides seed funding of up to $150K for projects leveraging artificial intelligence and machine learning to tackle climate change mitigation and adaptation.</t>
+          <t>A seed grant program supporting research, tools, and datasets at the intersection of climate change and machine learning or artificial intelligence.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aims to build partnerships between academic researchers, non-profits, startups, and other companies. Currently has no active/future calls planned.</t>
+          <t>Currently has no active or planned future calls, though past cycles funded projects up to $150K.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Ignore</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2791,12 +2791,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>166f9b27c5e956f4</t>
+          <t>9cca09bd6a8caab0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Blue Dot Network Certification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Workflows" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Workflows'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,12 +440,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8d40238686713191</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Supplier Prequalification (2026-2028)</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>training, ICT training</t>
+          <t>training</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tender includes specific open categories for ICT system procurement, software, LAN/WAN services, and training on ICT security solutions.</t>
+          <t>Matched configured ICT keyword(s): training.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open to eligible firms; includes reserved categories for AGPO groups (Youth, Women, and PWDs) with a valid AGPO certificate.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pursue</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Digital Health &amp; Climate Tech</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, climate technology Africa funding, grant application</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Active grant program supporting research and deployment at the intersection of climate change and machine learning.</t>
+          <t>Matched configured ICT keyword(s): machine learning.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Supports impactful projects involving dataset creation, deployment, and research utilizing ML to tackle climate change.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,27 +852,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>grant application, funding opportunity, machine learning, artificial intelligence</t>
+          <t>analysis, machine learning, artificial intelligence, training</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A seed grant program supporting research, tools, and datasets at the intersection of climate change and machine learning or artificial intelligence.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Currently has no active or planned future calls, though past cycles funded projects up to $150K.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ignore</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1032,79 +1032,8 @@
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>9b0fded721a6ff45</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Standard Tender Documents – Public Procurement Regulatory Authority × Close Close × Close Close × Close loading... File Properties Name File Uploader Folder PPA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://ppra.go.ke/standard-tender-documents</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Public Procurement Regulatory Authority</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>training</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Matched configured ICT keyword(s): training.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Review source document for eligibility requirements.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Project team</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1403,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1609,7 +1538,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.bluedot-network.org/certification</t>
+          <t>https://www.bluedot-network.org/certification, https://www.bluedot-network.org/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1662,31 +1591,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bluedot-network.org</t>
+          <t>User submitted</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.bluedot-network.org/</t>
+          <t>https://example.gov/tenders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>managed_source</t>
+          <t>Pending review</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Every monitor run</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Submitted 2026-08-10T09:15:56.399Z</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1696,7 +1625,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://example.gov/tenders</t>
+          <t>https://example.org/funding</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1725,7 +1654,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://example.org/funding</t>
+          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1742,7 +1671,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
+          <t>Submitted 2026-08-10T10:04:59.643Z</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1683,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
+          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1771,7 +1700,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-10T10:04:59.643Z</t>
+          <t>Submitted 2026-08-10T10:11:01.745Z</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1712,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
+          <t>https://www.bluedot-network.org/certification</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1800,7 +1729,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-10T10:11:01.745Z</t>
+          <t>Submitted 2026-08-11T16:20:04.680Z</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1741,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.bluedot-network.org/certification</t>
+          <t>https://www.climatechange.ai/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1829,7 +1758,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-11T16:20:04.680Z</t>
+          <t>Submitted 2026-08-11T18:24:37.612Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1770,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/</t>
+          <t>https://le.ac.uk/study/international-students/countries/africa/kenya?utm_source=google-search&amp;utm_medium=paid&amp;utm_campaign=international-recruitment-2026&amp;utm_content=brand_ug-pg-ke&amp;gad_source=1&amp;gad_campaignid=22138204529&amp;gbraid=0AAAAA-Jv9mK-HMbYwd0xUiIwJsYXujvIu&amp;gclid=CjwKCAjw4dDTBhAqEiwAkHYmSix5GlL4etFz30Inndq4q0FUkb21c040s1XsfJ6nm0XAcefOUWDscRoCxsgQAvD_BwE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1858,41 +1787,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Submitted 2026-08-11T18:24:37.612Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://le.ac.uk/study/international-students/countries/africa/kenya?utm_source=google-search&amp;utm_medium=paid&amp;utm_campaign=international-recruitment-2026&amp;utm_content=brand_ug-pg-ke&amp;gad_source=1&amp;gad_campaignid=22138204529&amp;gbraid=0AAAAA-Jv9mK-HMbYwd0xUiIwJsYXujvIu&amp;gclid=CjwKCAjw4dDTBhAqEiwAkHYmSix5GlL4etFz30Inndq4q0FUkb21c040s1XsfJ6nm0XAcefOUWDscRoCxsgQAvD_BwE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>Submitted 2026-08-11T19:52:46.857Z</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2529,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2581,12 +2481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8d40238686713191</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Supplier Prequalification (2026-2028)</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2600,7 +2500,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2651,12 +2551,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9b0fded721a6ff45</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standard Tender Documents – Public Procurement Regulatory Authority × Close Close × Close Close × Close loading... File Properties Name File Uploader Folder PPA</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2679,19 +2579,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://ppra.go.ke/standard-tender-documents</t>
+          <t>https://www.climatechange.ai/calls</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f7683a8e4ad35977</t>
+          <t>17124d19bfc6b3cd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Climate Change AI Grant Calls</t>
+          <t>Climate Change AI Innovation Grants</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2714,19 +2614,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/calls</t>
+          <t>https://www.climatechange.ai/innovation_grants</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17124d19bfc6b3cd</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grants</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2749,19 +2649,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/innovation_grants</t>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aa16da3072f3ff5b</t>
+          <t>9cca09bd6a8caab0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
+          <t>Blue Dot Network Certification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2775,7 +2675,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2784,19 +2684,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
+          <t>https://www.bluedot-network.org/certification</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9cca09bd6a8caab0</t>
+          <t>3c2462dbed3db6a6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Dot Network Certification</t>
+          <t>OECD InfraDays 2026 Highlights the Growing Global Momentum Behind Blue Dot Network Certification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2819,47 +2719,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.bluedot-network.org/certification</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3c2462dbed3db6a6</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>OECD InfraDays 2026 Highlights the Growing Global Momentum Behind Blue Dot Network Certification</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Review proposal and assign a bid decision</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Project team</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.bluedot-network.org/news/bdn-certificationceremony</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -445,7 +445,7 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -540,17 +540,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bc97777e6c0833cb</t>
+          <t>f9fb9cda54240283</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice.pdf</t>
+          <t>Open University of Kenya Prequalification and Tender Notice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>training, ICT training</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): training.</t>
+          <t>Tender includes pre-qualification for firms providing ICT Management Consulting, ICT Systems Audit, and Training on ICT Security Solutions (Category OUK/026/OP/2026-2028).</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Open to all interested and eligible firms. Certain reserved categories require valid AGPO certificates.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Pursue</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -680,17 +680,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aa16da3072f3ff5b</t>
+          <t>ce8ef9e770e3db15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
+          <t>Climate Change AI Announces Innovation Grantees</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Digital Health &amp; Climate Tech</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>analysis, machine learning, training</t>
+          <t>artificial intelligence, machine learning, funding opportunity, grant application</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): analysis, machine learning, training.</t>
+          <t>Press release detailing active and previously funded AI and machine learning projects under the Climate Change AI Innovation Grants.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Focuses on cross-sectoral teams leveraging AI/ML for climate mitigation and adaptation.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Digital Health &amp; Climate Tech</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning, artificial intelligence, grant application, funding opportunity, climate technology Africa funding</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): machine learning.</t>
+          <t>This is a genuine funding program that supports research, deployment, and dataset creation at the intersection of climate change and machine learning/AI.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Supports impactful work integrating machine learning and climate change. Current/upcoming programs include Innovation Grants 2025 (currently invitation only).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Data science</t>
+          <t>Digital Health &amp; Climate Tech</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>analysis, machine learning, artificial intelligence, training</t>
+          <t>artificial intelligence, machine learning, funding opportunity, grant application</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
+          <t>Offers seed grants for projects leveraging machine learning and AI to tackle climate change challenges.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Review source document for eligibility requirements.</t>
+          <t>Enables partnerships between academic researchers, non-profits, startups, and governmental organizations.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2481,12 +2481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bc97777e6c0833cb</t>
+          <t>f9fb9cda54240283</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice.pdf</t>
+          <t>Open University of Kenya Prequalification and Tender Notice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aa16da3072f3ff5b</t>
+          <t>ce8ef9e770e3db15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
+          <t>Climate Change AI Announces Innovation Grantees</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -540,17 +540,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f9fb9cda54240283</t>
+          <t>7b06c862b59f701e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Prequalification and Tender Notice</t>
+          <t>Open University of Kenya Tender Notice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>training, ICT training</t>
+          <t>training</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tender includes pre-qualification for firms providing ICT Management Consulting, ICT Systems Audit, and Training on ICT Security Solutions (Category OUK/026/OP/2026-2028).</t>
+          <t>Includes tenders for Enterprise Business Systems (ERP), Consultancy on E-Learning, and crucially Category OUK/026/OP/2026-2028: 'Training on ICT Security Solutions'.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open to all interested and eligible firms. Certain reserved categories require valid AGPO certificates.</t>
+          <t>Open to all interested and eligible firms, with specific reservation categories for AGPO groups (Youth, Women, and PWDs) with valid certification.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -680,12 +680,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ce8ef9e770e3db15</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climate Change AI Announces Innovation Grantees</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
+          <t>https://www.climatechange.ai/calls</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>artificial intelligence, machine learning, funding opportunity, grant application</t>
+          <t>machine learning, artificial intelligence, funding opportunity, grant application</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Press release detailing active and previously funded AI and machine learning projects under the Climate Change AI Innovation Grants.</t>
+          <t>The page lists current and past grant programs specifically focused on supporting research, deployment, and dataset creation at the intersection of climate change and machine learning/AI.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Focuses on cross-sectoral teams leveraging AI/ML for climate mitigation and adaptation.</t>
+          <t>Supports impactful work using AI and ML for climate change solutions, though specific current call details require contacting the provider or monitoring for open rounds.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -751,12 +751,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f7683a8e4ad35977</t>
+          <t>60c52eb38ad60cf3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Climate Change AI Grant Calls</t>
+          <t>Climate Change AI Innovation Grantees Announcement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/calls</t>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, grant application, funding opportunity, climate technology Africa funding</t>
+          <t>machine learning, artificial intelligence, funding opportunity, grant application</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>This is a genuine funding program that supports research, deployment, and dataset creation at the intersection of climate change and machine learning/AI.</t>
+          <t>Provides details and profiles on active/past funding opportunities under the Climate Change AI Innovation Grants program, which focuses on machine learning solutions.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Supports impactful work integrating machine learning and climate change. Current/upcoming programs include Innovation Grants 2025 (currently invitation only).</t>
+          <t>Historically supports cross-sectoral teams developing AI tools and open datasets. Call is currently closed but profiles past successful criteria.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>artificial intelligence, machine learning, funding opportunity, grant application</t>
+          <t>machine learning, artificial intelligence, grant application, funding opportunity</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Offers seed grants for projects leveraging machine learning and AI to tackle climate change challenges.</t>
+          <t>A genuine funding opportunity supporting research and deployment projects that leverage artificial intelligence and machine learning to tackle climate change.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Enables partnerships between academic researchers, non-profits, startups, and governmental organizations.</t>
+          <t>Supports cross-sectoral teams including academic researchers, non-profits, startups, and governmental organizations. Currently no future calls are planned, but open to partnerships.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2481,12 +2481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f9fb9cda54240283</t>
+          <t>7b06c862b59f701e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Prequalification and Tender Notice</t>
+          <t>Open University of Kenya Tender Notice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ce8ef9e770e3db15</t>
+          <t>60c52eb38ad60cf3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Announces Innovation Grantees</t>
+          <t>Climate Change AI Innovation Grantees Announcement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/proposal_output/proposals.xlsx
+++ b/proposal_output/proposals.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proposals'!$A$1:$O$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Workplan'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website Register'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keywords'!$A$1:$D$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Content Calendar'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Workflow Queue'!$A$1:$G$8</definedName>
@@ -445,7 +445,7 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7b06c862b59f701e</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Includes tenders for Enterprise Business Systems (ERP), Consultancy on E-Learning, and crucially Category OUK/026/OP/2026-2028: 'Training on ICT Security Solutions'.</t>
+          <t>Matched configured ICT keyword(s): training.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Open to all interested and eligible firms, with specific reservation categories for AGPO groups (Youth, Women, and PWDs) with valid certification.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pursue</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -680,22 +680,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f7683a8e4ad35977</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climate Change AI Grant Calls</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Digital Health &amp; Climate Tech</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/calls</t>
+          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, funding opportunity, grant application</t>
+          <t>analysis, machine learning, training</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The page lists current and past grant programs specifically focused on supporting research, deployment, and dataset creation at the intersection of climate change and machine learning/AI.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, training.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Supports impactful work using AI and ML for climate change solutions, though specific current call details require contacting the provider or monitoring for open rounds.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -751,22 +751,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>60c52eb38ad60cf3</t>
+          <t>f7683a8e4ad35977</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grantees Announcement</t>
+          <t>Climate Change AI Grant Calls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Digital Health &amp; Climate Tech</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.climatechange.ai/press_releases/2026-04-29/release</t>
+          <t>https://www.climatechange.ai/calls</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, funding opportunity, grant application</t>
+          <t>machine learning</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Provides details and profiles on active/past funding opportunities under the Climate Change AI Innovation Grants program, which focuses on machine learning solutions.</t>
+          <t>Matched configured ICT keyword(s): machine learning.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Historically supports cross-sectoral teams developing AI tools and open datasets. Call is currently closed but profiles past successful criteria.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Digital Health &amp; Climate Tech</t>
+          <t>Data science</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>machine learning, artificial intelligence, grant application, funding opportunity</t>
+          <t>analysis, machine learning, artificial intelligence, training</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A genuine funding opportunity supporting research and deployment projects that leverage artificial intelligence and machine learning to tackle climate change.</t>
+          <t>Matched configured ICT keyword(s): analysis, machine learning, artificial intelligence, training.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Supports cross-sectoral teams including academic researchers, non-profits, startups, and governmental organizations. Currently no future calls are planned, but open to partnerships.</t>
+          <t>Review source document for eligibility requirements.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1588,211 +1588,8 @@
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://example.gov/tenders</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://example.org/funding</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T09:15:56.399Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T10:04:59.643Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.climatechange.ai/papers/neurips2024/98https://www.climatechange.ai/papers/neurips2024/98</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-10T10:11:01.745Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.bluedot-network.org/certification</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-11T16:20:04.680Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://www.climatechange.ai/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-11T18:24:37.612Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>User submitted</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://le.ac.uk/study/international-students/countries/africa/kenya?utm_source=google-search&amp;utm_medium=paid&amp;utm_campaign=international-recruitment-2026&amp;utm_content=brand_ug-pg-ke&amp;gad_source=1&amp;gad_campaignid=22138204529&amp;gbraid=0AAAAA-Jv9mK-HMbYwd0xUiIwJsYXujvIu&amp;gclid=CjwKCAjw4dDTBhAqEiwAkHYmSix5GlL4etFz30Inndq4q0FUkb21c040s1XsfJ6nm0XAcefOUWDscRoCxsgQAvD_BwE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Pending review</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Submitted 2026-08-11T19:52:46.857Z</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2481,12 +2278,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7b06c862b59f701e</t>
+          <t>bc97777e6c0833cb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open University of Kenya Tender Notice</t>
+          <t>Open University of Kenya Tender Notice.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2621,12 +2418,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>60c52eb38ad60cf3</t>
+          <t>aa16da3072f3ff5b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Climate Change AI Innovation Grantees Announcement</t>
+          <t>Climate Change AI Announces Innovation Grantees (April 29, 2026) | Climate Change AI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2640,7 +2437,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
